--- a/Result/profitability/5213.xlsx
+++ b/Result/profitability/5213.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.08</v>
       </c>
       <c r="M2" t="n">
-        <v>0.61875</v>
+        <v>0.7174999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>28.57625</v>
+        <v>29.08</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.37</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7112499999999999</v>
+        <v>0.4887499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>28.38625</v>
+        <v>28.51125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.44</v>
       </c>
       <c r="M4" t="n">
-        <v>0.49125</v>
+        <v>0.35</v>
       </c>
       <c r="N4" t="n">
-        <v>28.39625</v>
+        <v>28.865</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.52</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3624999999999999</v>
+        <v>0.3849999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>27.5775</v>
+        <v>28.5125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,13 +1137,13 @@
         <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3825</v>
+        <v>0.4674999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>28.34125</v>
+        <v>28.525</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5474999999999999</v>
+        <v>0.3962499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>26.355</v>
+        <v>26.935</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.83</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4475</v>
+        <v>0.5149999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>26.48875</v>
+        <v>26.845</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5213</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3362</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2284</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1078</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="G75" t="n">
+        <v>697</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>20.72%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-23</v>
+      </c>
+      <c r="J75" t="n">
+        <v>674</v>
+      </c>
+      <c r="K75" t="n">
+        <v>300</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.66125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.8975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.849999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09760273972602729</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.479999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3044363044363043</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
